--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV19_recovery_validation_plot_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV19_recovery_validation_plot_data.xlsx
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
@@ -617,10 +617,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03921568627450978</v>
+        <v>0.09090909090909094</v>
       </c>
     </row>
     <row r="3">
@@ -628,27 +628,27 @@
         <v>53</v>
       </c>
       <c r="B3" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3529411764705882</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -657,58 +657,58 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.6818181818181819</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.6818181818181819</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2549019607843137</v>
+        <v>0.2651515151515151</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7450980392156863</v>
+        <v>0.7348484848484849</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -717,38 +717,38 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7878787878787878</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.196078431372549</v>
+        <v>0.1590909090909091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.803921568627451</v>
+        <v>0.8409090909090909</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67</v>
+        <v>272</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -757,18 +757,18 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1060606060606061</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8939393939393939</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70</v>
+        <v>487</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -777,18 +777,18 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1568627450980392</v>
+        <v>0.05303030303030304</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.946969696969697</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>71</v>
+        <v>625</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -797,149 +797,9 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1372549019607843</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8627450980392157</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>97</v>
-      </c>
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1176470588235294</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>108</v>
-      </c>
-      <c r="B13" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.09803921568627452</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.9019607843137255</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>139</v>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.09803921568627452</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.9019607843137255</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>157</v>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0735294117647059</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.9264705882352942</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>253</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.04901960784313727</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.9509803921568627</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>262</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.02450980392156863</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9754901960784313</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>424</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1111,31 +971,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8910053086246883</v>
+        <v>0.7536078466345479</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9963129840206002</v>
+        <v>0.99064824750947</v>
       </c>
       <c r="K2" t="n">
         <v>48</v>
@@ -1144,16 +1004,16 @@
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -1162,19 +1022,19 @@
         <v>11</v>
       </c>
       <c r="S2" t="n">
-        <v>5.81855420565098e-05</v>
+        <v>4.654843364520784e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00107061397383978</v>
+        <v>0.000861146022436345</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02127659574468085</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06382978723404255</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06382978723404255</v>
+        <v>0</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1186,7 +1046,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1195,10 +1055,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -1208,31 +1068,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9811320754716981</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9005685649885059</v>
+        <v>0.7900841350594088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9966616326132506</v>
+        <v>0.9922835330378734</v>
       </c>
       <c r="K3" t="n">
         <v>48</v>
@@ -1241,16 +1101,16 @@
         <v>9</v>
       </c>
       <c r="M3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="Q3" t="n">
         <v>0.8888888888888888</v>
@@ -1262,16 +1122,16 @@
         <v>9.309686729041568e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001908485779453521</v>
+        <v>0.001885211562630917</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01923076923076923</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="W3" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1283,7 +1143,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1292,10 +1152,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.333333333333333</v>
+        <v>2.888888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -1305,70 +1165,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9803921568627451</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8969519232441061</v>
+        <v>0.7820151050048196</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9965303967465577</v>
+        <v>0.9919307806988522</v>
       </c>
       <c r="K4" t="n">
         <v>53</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002199413489736071</v>
+        <v>0.002071405297211749</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002478704091607318</v>
+        <v>0.00279290601871247</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1380,7 +1240,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1389,10 +1249,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>197</v>
+        <v>142</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.714285714285714</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5">
@@ -1402,31 +1262,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9795918367346939</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8930623153224584</v>
+        <v>0.7820151050048196</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9963884204614692</v>
+        <v>0.9919307806988522</v>
       </c>
       <c r="K5" t="n">
         <v>53</v>
@@ -1435,37 +1295,37 @@
         <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1714285714285714</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003339850114043663</v>
+        <v>0.002595075175720337</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002164502164502165</v>
+        <v>0.001419727226178839</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1477,7 +1337,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1486,10 +1346,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>206</v>
+        <v>110</v>
       </c>
       <c r="AC5" t="n">
-        <v>5</v>
+        <v>3.142857142857143</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV19_recovery_validation_plot_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV19_recovery_validation_plot_data.xlsx
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -745,7 +745,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1219,7 +1219,7 @@
         <v>0.002071405297211749</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00279290601871247</v>
+        <v>0.002862728669180282</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV19_recovery_validation_plot_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV19_recovery_validation_plot_data.xlsx
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV19_recovery_validation_plot_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV19_recovery_validation_plot_data.xlsx
@@ -452,7 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
